--- a/INSTANCES/instances_xlsx/A_MTN_1/57FL_2A_2.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_1/57FL_2A_2.xlsx
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
